--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7769673E-7A22-407B-BB69-7D747D056372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E445BEC4-33C5-4866-A0FD-2B6A1EE0A245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="241">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1054,6 +1054,14 @@
   </si>
   <si>
     <t>三分块六乘法减少非二次幂小块的乘法次数，优化q/z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H79.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>160系数小块按64＋96分块，复用最高块乘积，优化q/z/gen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1486,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3377,20 +3385,37 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C111" s="1" t="s">
+      <c r="B111" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C111" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E111" s="3" t="s">
+      <c r="D111" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E111" s="4" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E445BEC4-33C5-4866-A0FD-2B6A1EE0A245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6630A299-AC18-421D-8336-C7DA2E77AFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="243">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1062,6 +1062,14 @@
   </si>
   <si>
     <t>160系数小块按64＋96分块，复用最高块乘积，优化q/z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复用160系数乘法的输入块和与结果重组公共项，减少重复异或，优化q/z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H80.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1494,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3418,6 +3426,23 @@
         <v>240</v>
       </c>
     </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6630A299-AC18-421D-8336-C7DA2E77AFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3129B3C8-702F-4649-B6FD-53B0907576D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="245">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1065,11 +1065,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>复用160系数乘法的输入块和与结果重组公共项，减少重复异或，优化q/z/gen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>diandeng10_a_faster2_png_H80.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H81.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裁剪递归乘法的高位零块，缩小子问题并跳过零乘积，优化q/x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复用160系数乘法的输入块和与结果重组公共项，优化q/z/gen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1502,7 +1510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3428,7 +3436,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>154</v>
@@ -3440,7 +3448,24 @@
         <v>1</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3129B3C8-702F-4649-B6FD-53B0907576D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DB7E20-E212-45FA-A9BA-58FE4A169725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="247">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1078,6 +1078,14 @@
   </si>
   <si>
     <t>复用160系数乘法的输入块和与结果重组公共项，优化q/z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H82.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剔除高位零块后按有效长度重新分块，减少q阶段乘法次数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1510,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3468,6 +3476,23 @@
         <v>243</v>
       </c>
     </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DB7E20-E212-45FA-A9BA-58FE4A169725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E2D2D9-A5F1-4D82-91E0-C332EA4444F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="249">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1086,6 +1086,14 @@
   </si>
   <si>
     <t>剔除高位零块后按有效长度重新分块，减少q阶段乘法次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>递归应用奇偶分解，各层共用单一工作区，减少z/gen卷积计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H83.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1518,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3493,6 +3501,23 @@
         <v>246</v>
       </c>
     </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E2D2D9-A5F1-4D82-91E0-C332EA4444F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D604EEC1-2A9C-483C-87F6-643E1CF0FA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="251">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1094,6 +1094,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H83.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合并Euclid消元，更新余式和Bézout系数，优化q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H84.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1526,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3518,6 +3526,23 @@
         <v>247</v>
       </c>
     </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D604EEC1-2A9C-483C-87F6-643E1CF0FA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BA15FF-C6DB-4B77-890C-96CAE85F4662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="253">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1102,6 +1102,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H84.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扩展欧几里得高位窗口至64系数，复用矩阵乘法公共计算，优化q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H85.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1534,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3543,6 +3551,23 @@
         <v>249</v>
       </c>
     </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BA15FF-C6DB-4B77-890C-96CAE85F4662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558969D5-DCAC-4C45-872E-7A8FCB584074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="255">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1110,6 +1110,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H85.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用64项联合表复用批量消元乘法，配合增大半GCD叶节点，优化q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H86.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1542,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3568,6 +3576,23 @@
         <v>251</v>
       </c>
     </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558969D5-DCAC-4C45-872E-7A8FCB584074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E96CAC-E6C4-46AE-985A-53FBE2717370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="257">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1118,6 +1118,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H86.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用Fibonacci反射倍增与多项式交换律，将z/gen降为O(n log n)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H87.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1550,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3593,6 +3601,23 @@
         <v>253</v>
       </c>
     </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E96CAC-E6C4-46AE-985A-53FBE2717370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65311E75-A6AF-4427-A539-C28EFD6C90E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="259">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1126,6 +1126,14 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H87.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H88.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Uᵃ(U+1)ᵇ 因子前缀异或替代分块除法，优化 x</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1558,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3618,6 +3626,23 @@
         <v>255</v>
       </c>
     </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65311E75-A6AF-4427-A539-C28EFD6C90E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98767666-F7E9-4E30-B9A0-3D944E9AE8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="261">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1133,7 +1133,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Uᵃ(U+1)ᵇ 因子前缀异或替代分块除法，优化 x</t>
+    <t>diandeng10_a_faster2_png_H89.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ᵃ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(U+1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ᵇ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 因子前缀异或替代分块除法，优化 x</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系数展开与反射移位的 LongWord 并行实现，优化 B 的 q/z/gen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1141,7 +1193,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1205,6 +1257,13 @@
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1566,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3640,7 +3699,24 @@
         <v>1</v>
       </c>
       <c r="E121" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
         <v>258</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98767666-F7E9-4E30-B9A0-3D944E9AE8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F51A09-4E0A-4ABD-9F04-E36E67D9DE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="263">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1186,6 +1186,14 @@
   </si>
   <si>
     <t>系数展开与反射移位的 LongWord 并行实现，优化 B 的 q/z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用 Frobenius 压缩分母，按余数类拆分并复用短除法，优化部分奇异 x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H90.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1625,7 +1633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3719,6 +3727,23 @@
         <v>260</v>
       </c>
     </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F51A09-4E0A-4ABD-9F04-E36E67D9DE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64A2EA7-3C7C-40D2-AA38-3C6E987B8A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="269">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1194,6 +1194,30 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H90.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用求和多项式恒等式和线性恢复优化z，分离移位边界优化A版z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H91.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H92.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复用联合表及向量块地址、展开建表并复用有界工作区，优化 q/g</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O(n^1.465)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引入GF(2)三分五乘及线性精确插值，降低q/g及一般x恢复的复杂度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1633,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3744,6 +3768,57 @@
         <v>261</v>
       </c>
     </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64A2EA7-3C7C-40D2-AA38-3C6E987B8A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AB2B3A-E484-48EE-BFDF-4A64BFC77E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="273">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1218,6 +1218,22 @@
   </si>
   <si>
     <t>引入GF(2)三分五乘及线性精确插值，降低q/g及一般x恢复的复杂度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H93.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H94.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O(n log²n log log n)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引入 GF(2) 精确递归三进制 FFT，大规模截断乘法，降低 q 及 x 恢复的复杂度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1657,19 +1673,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F126"/>
-  <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F127"/>
+  <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="58.75" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="36.375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>118</v>
       </c>
@@ -1686,7 +1702,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -1703,7 +1719,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1720,7 +1736,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
@@ -1737,7 +1753,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>75</v>
       </c>
@@ -1754,7 +1770,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>76</v>
       </c>
@@ -1771,7 +1787,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
@@ -1788,7 +1804,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>79</v>
       </c>
@@ -1805,7 +1821,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>80</v>
       </c>
@@ -1822,7 +1838,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>81</v>
       </c>
@@ -1839,7 +1855,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>82</v>
       </c>
@@ -1856,7 +1872,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>83</v>
       </c>
@@ -1873,7 +1889,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>84</v>
       </c>
@@ -1890,7 +1906,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>85</v>
       </c>
@@ -1907,7 +1923,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>86</v>
       </c>
@@ -1924,7 +1940,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>87</v>
       </c>
@@ -1941,7 +1957,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>88</v>
       </c>
@@ -1958,7 +1974,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>89</v>
       </c>
@@ -1975,7 +1991,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -1992,7 +2008,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>90</v>
       </c>
@@ -2009,7 +2025,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>91</v>
       </c>
@@ -2027,7 +2043,7 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>92</v>
       </c>
@@ -2045,7 +2061,7 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>93</v>
       </c>
@@ -2063,7 +2079,7 @@
       </c>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>94</v>
       </c>
@@ -2081,7 +2097,7 @@
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>95</v>
       </c>
@@ -2099,7 +2115,7 @@
       </c>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>96</v>
       </c>
@@ -2117,7 +2133,7 @@
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>97</v>
       </c>
@@ -2135,7 +2151,7 @@
       </c>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>98</v>
       </c>
@@ -2153,7 +2169,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>99</v>
       </c>
@@ -2170,7 +2186,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>100</v>
       </c>
@@ -2187,7 +2203,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>101</v>
       </c>
@@ -2204,7 +2220,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>102</v>
       </c>
@@ -2221,7 +2237,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>103</v>
       </c>
@@ -2238,7 +2254,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>104</v>
       </c>
@@ -2255,7 +2271,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>105</v>
       </c>
@@ -2272,7 +2288,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>106</v>
       </c>
@@ -2289,7 +2305,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>107</v>
       </c>
@@ -2306,7 +2322,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>108</v>
       </c>
@@ -2323,7 +2339,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>109</v>
       </c>
@@ -2340,7 +2356,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>110</v>
       </c>
@@ -2357,7 +2373,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>111</v>
       </c>
@@ -2374,7 +2390,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>112</v>
       </c>
@@ -2391,7 +2407,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>113</v>
       </c>
@@ -2408,7 +2424,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
@@ -2425,7 +2441,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>115</v>
       </c>
@@ -2442,7 +2458,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>116</v>
       </c>
@@ -2459,7 +2475,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>49</v>
       </c>
@@ -2476,7 +2492,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>50</v>
       </c>
@@ -2493,7 +2509,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>51</v>
       </c>
@@ -2510,7 +2526,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>52</v>
       </c>
@@ -2527,7 +2543,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>53</v>
       </c>
@@ -2544,7 +2560,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>54</v>
       </c>
@@ -2561,7 +2577,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>55</v>
       </c>
@@ -2578,7 +2594,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>56</v>
       </c>
@@ -2595,7 +2611,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>57</v>
       </c>
@@ -2612,7 +2628,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>58</v>
       </c>
@@ -2629,7 +2645,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>59</v>
       </c>
@@ -2646,7 +2662,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>60</v>
       </c>
@@ -2663,7 +2679,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>61</v>
       </c>
@@ -2680,7 +2696,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>62</v>
       </c>
@@ -2697,7 +2713,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>63</v>
       </c>
@@ -2714,7 +2730,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>64</v>
       </c>
@@ -2731,7 +2747,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>65</v>
       </c>
@@ -2748,7 +2764,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>66</v>
       </c>
@@ -2765,7 +2781,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>67</v>
       </c>
@@ -2782,7 +2798,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>68</v>
       </c>
@@ -2799,7 +2815,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>69</v>
       </c>
@@ -2816,7 +2832,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>70</v>
       </c>
@@ -2833,7 +2849,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -2850,7 +2866,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>5</v>
       </c>
@@ -2867,7 +2883,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>6</v>
       </c>
@@ -2884,7 +2900,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>9</v>
       </c>
@@ -2901,7 +2917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>10</v>
       </c>
@@ -2918,7 +2934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>12</v>
       </c>
@@ -2935,7 +2951,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>14</v>
       </c>
@@ -2952,7 +2968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>16</v>
       </c>
@@ -2969,7 +2985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -2986,7 +3002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>21</v>
       </c>
@@ -3003,7 +3019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>22</v>
       </c>
@@ -3020,7 +3036,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>25</v>
       </c>
@@ -3037,7 +3053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>27</v>
       </c>
@@ -3054,7 +3070,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>29</v>
       </c>
@@ -3071,7 +3087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>31</v>
       </c>
@@ -3088,7 +3104,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>33</v>
       </c>
@@ -3105,7 +3121,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>35</v>
       </c>
@@ -3122,7 +3138,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>36</v>
       </c>
@@ -3139,7 +3155,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>39</v>
       </c>
@@ -3156,7 +3172,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>41</v>
       </c>
@@ -3173,7 +3189,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>43</v>
       </c>
@@ -3190,7 +3206,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>45</v>
       </c>
@@ -3207,7 +3223,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>47</v>
       </c>
@@ -3224,7 +3240,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>117</v>
       </c>
@@ -3241,7 +3257,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>200</v>
       </c>
@@ -3258,7 +3274,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>202</v>
       </c>
@@ -3275,7 +3291,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>204</v>
       </c>
@@ -3292,7 +3308,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>205</v>
       </c>
@@ -3326,7 +3342,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>212</v>
       </c>
@@ -3343,7 +3359,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>213</v>
       </c>
@@ -3360,7 +3376,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>215</v>
       </c>
@@ -3377,7 +3393,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>216</v>
       </c>
@@ -3394,7 +3410,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>219</v>
       </c>
@@ -3411,7 +3427,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>221</v>
       </c>
@@ -3428,7 +3444,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>223</v>
       </c>
@@ -3445,7 +3461,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>226</v>
       </c>
@@ -3462,7 +3478,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>225</v>
       </c>
@@ -3479,7 +3495,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>229</v>
       </c>
@@ -3496,7 +3512,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>231</v>
       </c>
@@ -3513,7 +3529,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>232</v>
       </c>
@@ -3530,7 +3546,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>236</v>
       </c>
@@ -3547,7 +3563,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>237</v>
       </c>
@@ -3564,7 +3580,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>239</v>
       </c>
@@ -3581,7 +3597,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>241</v>
       </c>
@@ -3598,7 +3614,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>242</v>
       </c>
@@ -3615,7 +3631,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>245</v>
       </c>
@@ -3632,7 +3648,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>248</v>
       </c>
@@ -3649,7 +3665,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>250</v>
       </c>
@@ -3666,7 +3682,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>252</v>
       </c>
@@ -3683,7 +3699,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>254</v>
       </c>
@@ -3700,7 +3716,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>256</v>
       </c>
@@ -3717,7 +3733,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>257</v>
       </c>
@@ -3734,7 +3750,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>258</v>
       </c>
@@ -3751,7 +3767,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>262</v>
       </c>
@@ -3768,7 +3784,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>264</v>
       </c>
@@ -3785,7 +3801,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>265</v>
       </c>
@@ -3802,9 +3818,9 @@
         <v>263</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>154</v>
@@ -3817,6 +3833,23 @@
       </c>
       <c r="E126" s="6" t="s">
         <v>268</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AB2B3A-E484-48EE-BFDF-4A64BFC77E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50252F30-19B8-42D5-8BC8-E7CC1F17171E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="15780" yWindow="3915" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="275">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1137,54 +1137,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>U</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ᵃ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(U+1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ᵇ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 因子前缀异或替代分块除法，优化 x</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>系数展开与反射移位的 LongWord 并行实现，优化 B 的 q/z/gen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1234,6 +1186,18 @@
   </si>
   <si>
     <t>引入 GF(2) 精确递归三进制 FFT，大规模截断乘法，降低 q 及 x 恢复的复杂度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H95.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对称周期压缩、求和核复用、末轮状态裁剪、GCD 指针交换及前缀异或优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uᵃ(U+1)ᵇ 因子前缀异或替代分块除法，优化 x</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1241,7 +1205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1305,13 +1269,6 @@
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1673,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3734,20 +3691,20 @@
       </c>
     </row>
     <row r="121" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C121" s="1" t="s">
+      <c r="B121" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>259</v>
+      <c r="D121" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3764,12 +3721,12 @@
         <v>1</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>154</v>
@@ -3781,12 +3738,12 @@
         <v>1</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>154</v>
@@ -3798,12 +3755,12 @@
         <v>1</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>154</v>
@@ -3815,41 +3772,58 @@
         <v>1</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C126" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E126" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C127" s="2" t="s">
+      <c r="D127" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E127" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E127" s="6" t="s">
+    </row>
+    <row r="128" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="4" t="s">
         <v>272</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50252F30-19B8-42D5-8BC8-E7CC1F17171E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F210DEA-B166-4B6F-9ED6-8D98C1B971BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15780" yWindow="3915" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="277">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1185,19 +1185,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>引入 GF(2) 精确递归三进制 FFT，大规模截断乘法，降低 q 及 x 恢复的复杂度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>diandeng10_a_faster2_png_H95.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对称周期压缩、求和核复用、末轮状态裁剪、GCD 指针交换及前缀异或优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Uᵃ(U+1)ᵇ 因子前缀异或替代分块除法，优化 x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H96.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GCD 小矩阵、对称半行恢复与镜像、批量清零复制及 F/C 倍增边界优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精确递归三进制 FFT，大规模截断乘法，降低 q 及 x 恢复的复杂度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对称周期压缩、求和核复用、末轮状态裁剪、GCD 指针交换及前缀异或</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1630,7 +1638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3704,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3806,24 +3814,41 @@
         <v>1</v>
       </c>
       <c r="E127" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C128" s="4" t="s">
+      <c r="B128" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D128" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E128" s="4" t="s">
+      <c r="D128" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="4" t="s">
         <v>273</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F210DEA-B166-4B6F-9ED6-8D98C1B971BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287A08F7-5345-49DA-A7C0-F670C5CA6690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="4545" yWindow="4545" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="280">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1206,6 +1206,18 @@
   </si>
   <si>
     <t>对称周期压缩、求和核复用、末轮状态裁剪、GCD 指针交换及前缀异或</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H97.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单缓冲区 U→H 展开与合并转换，优化 z；B 同步优化整字反射读取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H98.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1638,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3851,6 +3863,38 @@
         <v>274</v>
       </c>
     </row>
+    <row r="130" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E131" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287A08F7-5345-49DA-A7C0-F670C5CA6690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66833B42-5378-43CF-8120-1216D08F9BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="4545" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="283">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1218,6 +1218,18 @@
   </si>
   <si>
     <t>diandeng10_a_faster2_png_H98.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H99.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B 版递推边界判断外提、半段结果直接读取及二项式前缀异或固定移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B 版固定联合表构造展开、热点过程内联及位反转与隔位展开的字节查表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1650,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3893,7 +3905,26 @@
       <c r="D131" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E131" s="1"/>
+      <c r="E131" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66833B42-5378-43CF-8120-1216D08F9BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59ABFE4-61C7-4A4F-B800-8F410BF32DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="298">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1137,22 +1137,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>系数展开与反射移位的 LongWord 并行实现，优化 B 的 q/z/gen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>利用 Frobenius 压缩分母，按余数类拆分并复用短除法，优化部分奇异 x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>diandeng10_a_faster2_png_H90.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>利用求和多项式恒等式和线性恢复优化z，分离移位边界优化A版z/gen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>diandeng10_a_faster2_png_H91.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1161,18 +1149,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>复用联合表及向量块地址、展开建表并复用有界工作区，优化 q/g</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>O(n^1.465)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>引入GF(2)三分五乘及线性精确插值，降低q/g及一般x恢复的复杂度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>diandeng10_a_faster2_png_H93.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1197,26 +1177,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GCD 小矩阵、对称半行恢复与镜像、批量清零复制及 F/C 倍增边界优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>精确递归三进制 FFT，大规模截断乘法，降低 q 及 x 恢复的复杂度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对称周期压缩、求和核复用、末轮状态裁剪、GCD 指针交换及前缀异或</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>diandeng10_a_faster2_png_H97.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>单缓冲区 U→H 展开与合并转换，优化 z；B 同步优化整字反射读取</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>diandeng10_a_faster2_png_H98.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1225,12 +1189,89 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>B 版递推边界判断外提、半段结果直接读取及二项式前缀异或固定移</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B 版固定联合表构造展开、热点过程内联及位反转与隔位展开的字节查表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>diandeng10_a_faster2_png_H100.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H101.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H102.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H103.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H104.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H105.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H106.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整字并行展开与反射移位，优化B版q/z/gen</t>
+  </si>
+  <si>
+    <t>Frobenius压缩与余数类短除法，优化奇异x</t>
+  </si>
+  <si>
+    <t>复用联合表、块地址与工作区，优化q/g</t>
+  </si>
+  <si>
+    <t>求和恒等式优化z，分离A版z/gen移位边界</t>
+  </si>
+  <si>
+    <t>引入三分五乘与精确插值，降低q及一般x复杂度</t>
+  </si>
+  <si>
+    <t>引入精确三进制环FFT，降低q及一般x复杂度</t>
+  </si>
+  <si>
+    <t>对称压缩、核复用、状态裁剪、指针交换与前缀异或</t>
+  </si>
+  <si>
+    <t>GCD小矩阵、半行镜像、批量复制与F/C边界优化</t>
+  </si>
+  <si>
+    <t>合并U→H转换优化z，B版整字反射读取</t>
+  </si>
+  <si>
+    <t>B版边界外提、半段直读与固定移位前缀异或</t>
+  </si>
+  <si>
+    <t>B版联合表展开、热点内联、反转与隔位展开查表</t>
+  </si>
+  <si>
+    <t>引入四分七乘与精确插值，大规模保留环FFT</t>
+  </si>
+  <si>
+    <t>引入精确整数NTT，降低大规模乘法复杂度</t>
+  </si>
+  <si>
+    <t>按n分派后端，合并矩阵NTT并复用频域结果</t>
+  </si>
+  <si>
+    <t>n=2^k−1时线性直解与校验，首行Θ(n)</t>
+  </si>
+  <si>
+    <t>根集合、FWHT与加法FFT，降低特殊q复杂度</t>
+  </si>
+  <si>
+    <t>二项式分块与Taylor基转换，降低特殊q复杂度</t>
+  </si>
+  <si>
+    <t>小子域位平面转换，降低特殊q的字运算复杂度</t>
+  </si>
+  <si>
+    <t>O(n log²n)</t>
   </si>
 </sst>
 </file>
@@ -1662,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3736,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3753,12 +3794,12 @@
         <v>1</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>154</v>
@@ -3770,12 +3811,12 @@
         <v>1</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>154</v>
@@ -3787,12 +3828,12 @@
         <v>1</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>154</v>
@@ -3804,126 +3845,245 @@
         <v>1</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>154</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>274</v>
+      <c r="A129" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>282</v>
+      <c r="A132" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59ABFE4-61C7-4A4F-B800-8F410BF32DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6BBB46-6D45-4640-8F38-616ABEE382A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="304">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1253,9 +1253,6 @@
     <t>引入四分七乘与精确插值，大规模保留环FFT</t>
   </si>
   <si>
-    <t>引入精确整数NTT，降低大规模乘法复杂度</t>
-  </si>
-  <si>
     <t>按n分派后端，合并矩阵NTT并复用频域结果</t>
   </si>
   <si>
@@ -1272,6 +1269,30 @@
   </si>
   <si>
     <t>O(n log²n)</t>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H107.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H108.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H109.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持范围内启用精确整数NTT，加速大规模乘法</t>
+  </si>
+  <si>
+    <t>小逆元Frobenius提升，新增六类线性求解尺寸</t>
+  </si>
+  <si>
+    <t>反射余数分块，n+1奇数部分≤31时线性求解</t>
+  </si>
+  <si>
+    <t>复用叶输入、同步AB并清理不可达代码</t>
   </si>
 </sst>
 </file>
@@ -1703,7 +1724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3992,13 +4013,13 @@
         <v>154</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4009,13 +4030,13 @@
         <v>154</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4026,13 +4047,13 @@
         <v>154</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4043,13 +4064,13 @@
         <v>154</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4060,13 +4081,13 @@
         <v>154</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4077,13 +4098,64 @@
         <v>154</v>
       </c>
       <c r="C139" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E139" s="3" t="s">
+      <c r="B140" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>296</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6BBB46-6D45-4640-8F38-616ABEE382A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069B1197-D627-480A-A6C8-378E0A71C80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4200" yWindow="4200" windowWidth="28800" windowHeight="15345" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="305">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -412,14 +412,6 @@
   </si>
   <si>
     <t>diandeng10_m_test.pas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>diandeng11_test.pas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>diandeng11_test_strassen.pas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1293,6 +1285,18 @@
   </si>
   <si>
     <t>复用叶输入、同步AB并清理不可达代码</t>
+  </si>
+  <si>
+    <t>diandeng10_test.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_test_strassen.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H110.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1724,7 +1728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -1738,19 +1742,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1758,7 +1762,7 @@
         <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>72</v>
@@ -1767,7 +1771,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1775,7 +1779,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>72</v>
@@ -1784,7 +1788,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1792,7 +1796,7 @@
         <v>73</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>74</v>
@@ -1801,7 +1805,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1809,7 +1813,7 @@
         <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>74</v>
@@ -1818,7 +1822,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1826,16 +1830,16 @@
         <v>76</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1843,16 +1847,16 @@
         <v>78</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1860,16 +1864,16 @@
         <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1877,16 +1881,16 @@
         <v>80</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1894,16 +1898,16 @@
         <v>81</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1911,7 +1915,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>0</v>
@@ -1920,7 +1924,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1928,7 +1932,7 @@
         <v>83</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>0</v>
@@ -1937,7 +1941,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1945,7 +1949,7 @@
         <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>0</v>
@@ -1954,7 +1958,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1962,7 +1966,7 @@
         <v>85</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>0</v>
@@ -1971,7 +1975,7 @@
         <v>30</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1979,7 +1983,7 @@
         <v>86</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>0</v>
@@ -1988,7 +1992,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1996,7 +2000,7 @@
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>0</v>
@@ -2005,7 +2009,7 @@
         <v>30</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2013,7 +2017,7 @@
         <v>88</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>0</v>
@@ -2022,7 +2026,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2030,7 +2034,7 @@
         <v>89</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>0</v>
@@ -2039,7 +2043,7 @@
         <v>30</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2047,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>0</v>
@@ -2056,7 +2060,7 @@
         <v>30</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2064,7 +2068,7 @@
         <v>90</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>0</v>
@@ -2073,7 +2077,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2081,7 +2085,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>0</v>
@@ -2090,7 +2094,7 @@
         <v>30</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F21" s="1"/>
     </row>
@@ -2099,7 +2103,7 @@
         <v>92</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>0</v>
@@ -2108,7 +2112,7 @@
         <v>30</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F22" s="1"/>
     </row>
@@ -2117,7 +2121,7 @@
         <v>93</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>0</v>
@@ -2126,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F23" s="1"/>
     </row>
@@ -2135,7 +2139,7 @@
         <v>94</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>0</v>
@@ -2144,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F24" s="1"/>
     </row>
@@ -2153,7 +2157,7 @@
         <v>95</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>0</v>
@@ -2162,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F25" s="1"/>
     </row>
@@ -2171,7 +2175,7 @@
         <v>96</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>0</v>
@@ -2180,52 +2184,52 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>97</v>
+        <v>302</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>0</v>
@@ -2234,15 +2238,15 @@
         <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>0</v>
@@ -2251,15 +2255,15 @@
         <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>0</v>
@@ -2268,15 +2272,15 @@
         <v>30</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>0</v>
@@ -2285,15 +2289,15 @@
         <v>30</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>0</v>
@@ -2302,15 +2306,15 @@
         <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>0</v>
@@ -2319,15 +2323,15 @@
         <v>30</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>0</v>
@@ -2336,15 +2340,15 @@
         <v>30</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>0</v>
@@ -2353,15 +2357,15 @@
         <v>30</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>0</v>
@@ -2370,15 +2374,15 @@
         <v>30</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>0</v>
@@ -2387,15 +2391,15 @@
         <v>30</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>30</v>
@@ -2404,15 +2408,15 @@
         <v>30</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>30</v>
@@ -2421,15 +2425,15 @@
         <v>30</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>30</v>
@@ -2438,15 +2442,15 @@
         <v>30</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>30</v>
@@ -2455,15 +2459,15 @@
         <v>30</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>30</v>
@@ -2472,15 +2476,15 @@
         <v>30</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>30</v>
@@ -2489,15 +2493,15 @@
         <v>30</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>30</v>
@@ -2506,15 +2510,15 @@
         <v>30</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>30</v>
@@ -2523,7 +2527,7 @@
         <v>30</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2531,7 +2535,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>30</v>
@@ -2540,7 +2544,7 @@
         <v>30</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2548,7 +2552,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>30</v>
@@ -2557,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2565,7 +2569,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>30</v>
@@ -2574,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2582,7 +2586,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>30</v>
@@ -2591,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2599,7 +2603,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>30</v>
@@ -2608,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2616,7 +2620,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>30</v>
@@ -2625,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2633,7 +2637,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>30</v>
@@ -2642,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2650,7 +2654,7 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>30</v>
@@ -2659,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2667,7 +2671,7 @@
         <v>57</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>30</v>
@@ -2676,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2684,7 +2688,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>30</v>
@@ -2693,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2701,7 +2705,7 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>30</v>
@@ -2710,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2718,7 +2722,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>30</v>
@@ -2727,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2735,7 +2739,7 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>30</v>
@@ -2744,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2752,7 +2756,7 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>30</v>
@@ -2761,7 +2765,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2769,7 +2773,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>30</v>
@@ -2778,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2786,7 +2790,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>30</v>
@@ -2795,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2803,7 +2807,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>30</v>
@@ -2812,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2820,7 +2824,7 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>30</v>
@@ -2829,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2837,7 +2841,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>30</v>
@@ -2846,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2854,7 +2858,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>30</v>
@@ -2863,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2871,7 +2875,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>30</v>
@@ -2880,7 +2884,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2888,7 +2892,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>30</v>
@@ -2897,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2905,7 +2909,7 @@
         <v>3</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>30</v>
@@ -2914,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2922,7 +2926,7 @@
         <v>5</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>30</v>
@@ -2939,7 +2943,7 @@
         <v>6</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>30</v>
@@ -2956,7 +2960,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>30</v>
@@ -2973,7 +2977,7 @@
         <v>10</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>30</v>
@@ -2990,7 +2994,7 @@
         <v>12</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>30</v>
@@ -3007,7 +3011,7 @@
         <v>14</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>30</v>
@@ -3024,7 +3028,7 @@
         <v>16</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>30</v>
@@ -3041,7 +3045,7 @@
         <v>19</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>30</v>
@@ -3058,7 +3062,7 @@
         <v>21</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>30</v>
@@ -3075,7 +3079,7 @@
         <v>22</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>30</v>
@@ -3092,7 +3096,7 @@
         <v>25</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>30</v>
@@ -3109,7 +3113,7 @@
         <v>27</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>30</v>
@@ -3126,7 +3130,7 @@
         <v>29</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>30</v>
@@ -3143,7 +3147,7 @@
         <v>31</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>30</v>
@@ -3160,7 +3164,7 @@
         <v>33</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>30</v>
@@ -3177,7 +3181,7 @@
         <v>35</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>30</v>
@@ -3194,7 +3198,7 @@
         <v>36</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>30</v>
@@ -3211,7 +3215,7 @@
         <v>39</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>30</v>
@@ -3228,7 +3232,7 @@
         <v>41</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>30</v>
@@ -3245,7 +3249,7 @@
         <v>43</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>30</v>
@@ -3262,7 +3266,7 @@
         <v>45</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>30</v>
@@ -3279,7 +3283,7 @@
         <v>47</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>30</v>
@@ -3293,10 +3297,10 @@
     </row>
     <row r="92" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>30</v>
@@ -3305,15 +3309,15 @@
         <v>1</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>30</v>
@@ -3322,15 +3326,15 @@
         <v>1</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>30</v>
@@ -3339,823 +3343,837 @@
         <v>1</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E96" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="D97" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
